--- a/Extras/2026-06-20 - Main results stats/mainresults.xlsx
+++ b/Extras/2026-06-20 - Main results stats/mainresults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Extras\2026-06-20 - Main results stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBCED76-E942-4C54-906B-F44C12EF9361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F89B0C9-FDED-44D7-97AB-21925B0D5C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="20">
   <si>
     <t>Uranium</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Fertile (n,gamma)</t>
+  </si>
+  <si>
+    <t>Nominal</t>
   </si>
 </sst>
 </file>
@@ -444,7 +447,7 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.3">
